--- a/output/评审详表.xlsx
+++ b/output/评审详表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>完整文件数</t>
+          <t>完整率</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>完整率</t>
+          <t>可复用</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>可复用</t>
+          <t>可执行</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>可执行</t>
+          <t>可验证</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>可验证</t>
+          <t>IO明确</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>IO明确</t>
+          <t>质量均分</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>均分</t>
+          <t>综合分</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>综合分</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>缺失项</t>
         </is>
@@ -475,10 +470,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -495,18 +492,13 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>0.97</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,40 +507,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
+      <c r="G3" t="n">
+        <v>0.62</v>
       </c>
       <c r="H3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Demo（视频/截图）、AI 生成日志</t>
+        <v>0.47</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Demo（视频/截图/演示）、AI 生成日志</t>
         </is>
       </c>
     </row>
@@ -561,8 +550,10 @@
       <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -571,7 +562,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>⚠️</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -579,20 +570,15 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
+      <c r="G4" t="n">
+        <v>0.25</v>
       </c>
       <c r="H4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.15</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Skill 说明文档、可执行内容、Demo（视频/截图）、教学说明、AI 生成日志</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Skill 说明文档、可执行内容、Demo（视频/截图/演示）、教学说明、AI 生成日志</t>
         </is>
       </c>
     </row>

--- a/output/评审详表.xlsx
+++ b/output/评审详表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
